--- a/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/trans.alpha.carotenes/Resultats_trans.alpha.carotenes_moy_R2.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,75 +362,80 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>LV0_R2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>LV1_R2</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>LV2_R2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>LV3_R2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LV4_R2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>LV5_R2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>LV6_R2</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>LV7_R2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>LV8_R2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>LV9_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>LV10_R2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LV11_R2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LV12_R2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LV13_R2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>LV14_R2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>LV15_R2</t>
         </is>
@@ -443,48 +448,51 @@
         </is>
       </c>
       <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
         <v>0.2741626654768903</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>0.4373312344393419</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>0.494250341451577</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>0.5382604204015959</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>0.6167408909189962</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>0.6492822574469049</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0.664351226991381</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>0.6761190239121542</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>0.7069685226691548</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.7368426183238108</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.7715612761946986</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.7968853278070047</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.820636239101395</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.8507940140811479</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>0.863402516457964</v>
       </c>
     </row>
@@ -495,48 +503,51 @@
         </is>
       </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.3420639652337399</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>0.4384733574054129</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>0.4891361357447678</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>0.5550186395683574</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>0.5856367529833126</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>0.6441236908140953</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0.6858440431027435</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>0.7228081810010603</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>0.7482687328450972</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.7670821462455328</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.7880994084577309</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.8134861102874049</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.8323475595671671</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.8545188630837884</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>0.8696885605773941</v>
       </c>
     </row>
@@ -547,48 +558,51 @@
         </is>
       </c>
       <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
         <v>0.2875094292691487</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>0.4127304934091831</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>0.4399809068780067</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>0.4937321710954582</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>0.5156871727814041</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>0.5570748165483397</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>0.5971017437471899</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>0.6374362401317336</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>0.6712729636168095</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.7130468224711626</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.7534945175533659</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.7875347342364837</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.808260708092799</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.8211874448987373</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>0.8383384433268899</v>
       </c>
     </row>
@@ -599,48 +613,51 @@
         </is>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
         <v>0.4073798092699187</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>0.4462208459443673</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>0.475748733836189</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>0.5165458828089873</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>0.5708160318633035</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.6359290945902127</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <v>0.6623525076141081</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>0.7138949215484743</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>0.7442589578353969</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.764113927233204</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.7893580113744457</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>0.8126752432791471</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>0.8381404860021548</v>
       </c>
-      <c r="O5">
+      <c r="P5">
         <v>0.8507410826541894</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>0.8731707672872562</v>
       </c>
     </row>
@@ -651,48 +668,51 @@
         </is>
       </c>
       <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
         <v>0.4076161095204525</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>0.4513098812412025</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>0.4774440356288082</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>0.5396990204160299</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>0.589827158492421</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>0.6270680577101966</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>0.6747070682313493</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>0.7117965260231562</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>0.7352638667300104</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>0.7493619536127534</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>0.7689767692415672</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <v>0.7998854868162748</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>0.8340848268905838</v>
       </c>
-      <c r="O6">
+      <c r="P6">
         <v>0.8525389772008753</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>0.8718878423589607</v>
       </c>
     </row>
@@ -703,48 +723,51 @@
         </is>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
         <v>0.2860651044394756</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>0.4244380400500439</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>0.5152102611834175</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>0.5510810335650566</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>0.6086767517655159</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.6197462316121362</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <v>0.6579258498053377</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>0.6877782631822484</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>0.7130223809156306</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.7408342081398915</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.7934978936841111</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <v>0.8271607247979867</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>0.8366717288366778</v>
       </c>
-      <c r="O7">
+      <c r="P7">
         <v>0.8521683354542948</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>0.8608240847197537</v>
       </c>
     </row>
@@ -755,48 +778,51 @@
         </is>
       </c>
       <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
         <v>0.3288556573400627</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>0.4062317411484052</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>0.4769102513958751</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>0.5236408866642439</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>0.5458355784817681</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>0.5987757928972213</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <v>0.6416159201753124</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>0.6718791198516798</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>0.709027334665123</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>0.7422943651009026</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>0.7762817834372878</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <v>0.7900940085877288</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <v>0.8104905192508906</v>
       </c>
-      <c r="O8">
+      <c r="P8">
         <v>0.8240370311734612</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>0.838248312966228</v>
       </c>
     </row>
@@ -807,48 +833,51 @@
         </is>
       </c>
       <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
         <v>0.3288052385932286</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>0.4060519211533591</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>0.4746253097185832</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>0.5188619706244681</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>0.5379865926287278</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>0.5861592114273714</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <v>0.6262814624159109</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>0.6445306695957052</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>0.6699896371644585</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.6924275525613646</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.719375402459866</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <v>0.7309968022732418</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <v>0.7460307335905296</v>
       </c>
-      <c r="O9">
+      <c r="P9">
         <v>0.7562929234252782</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>0.7882353530581052</v>
       </c>
     </row>
@@ -859,48 +888,51 @@
         </is>
       </c>
       <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
         <v>0.3287724316071924</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>0.4060245076492259</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>0.4744709123829463</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>0.5187547275195978</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>0.5379480479991789</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>0.5863712560801591</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>0.6269744463546285</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>0.6444167854867555</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>0.6693189989742447</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>0.6913203505945313</v>
       </c>
-      <c r="L10">
+      <c r="M10">
         <v>0.7190050356443882</v>
       </c>
-      <c r="M10">
+      <c r="N10">
         <v>0.7298475536019318</v>
       </c>
-      <c r="N10">
+      <c r="O10">
         <v>0.7438854382192985</v>
       </c>
-      <c r="O10">
+      <c r="P10">
         <v>0.7540843499735403</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>0.7796783211381473</v>
       </c>
     </row>
@@ -911,48 +943,51 @@
         </is>
       </c>
       <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
         <v>0.3288185248328195</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>0.406102504730299</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>0.4752282096469013</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>0.5196430215137933</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>0.5388169599546755</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>0.5856733545412256</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>0.6245317225670505</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>0.6438931799716376</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>0.6696205299605307</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.6933031988908618</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.7178158277948055</v>
       </c>
-      <c r="M11">
+      <c r="N11">
         <v>0.7305393329226142</v>
       </c>
-      <c r="N11">
+      <c r="O11">
         <v>0.7476708126600057</v>
       </c>
-      <c r="O11">
+      <c r="P11">
         <v>0.7563136771090812</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>0.7761109812049685</v>
       </c>
     </row>
@@ -963,48 +998,51 @@
         </is>
       </c>
       <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
         <v>0.4154033156141058</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>0.4547859957536942</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>0.4843000420898671</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>0.5390501179482441</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>0.5891177319239691</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>0.6570640176420188</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <v>0.6933607222128787</v>
       </c>
-      <c r="I12">
+      <c r="J12">
         <v>0.7381401806110726</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>0.7625758202209874</v>
       </c>
-      <c r="K12">
+      <c r="L12">
         <v>0.7763467032964552</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>0.8074344354581535</v>
       </c>
-      <c r="M12">
+      <c r="N12">
         <v>0.8232945922148545</v>
       </c>
-      <c r="N12">
+      <c r="O12">
         <v>0.839928552580026</v>
       </c>
-      <c r="O12">
+      <c r="P12">
         <v>0.8494453765519875</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>0.8663815453771101</v>
       </c>
     </row>
@@ -1015,48 +1053,51 @@
         </is>
       </c>
       <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
         <v>0.4183981169987373</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>0.4898985359770712</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>0.5351952682601521</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>0.5575908551814994</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>0.6016369849636366</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>0.6624292215208891</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>0.6904631629609923</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>0.7391556972527831</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>0.7685096722010926</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>0.7884560972731306</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>0.8013958739423064</v>
       </c>
-      <c r="M13">
+      <c r="N13">
         <v>0.8129471188629591</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.8251689826262765</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.8366711364204542</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>0.8489524514378843</v>
       </c>
     </row>
@@ -1067,48 +1108,51 @@
         </is>
       </c>
       <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
         <v>0.2860555821798199</v>
       </c>
-      <c r="C14">
+      <c r="D14">
         <v>0.4243533027555568</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>0.5146703330144042</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>0.5499692634185948</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>0.6060171008005443</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>0.6155183788087657</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>0.6471319433853722</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>0.6708472467143333</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>0.6892455785625164</v>
       </c>
-      <c r="K14">
+      <c r="L14">
         <v>0.7069199134411064</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>0.7425484914631597</v>
       </c>
-      <c r="M14">
+      <c r="N14">
         <v>0.7766442299862213</v>
       </c>
-      <c r="N14">
+      <c r="O14">
         <v>0.7877031013860947</v>
       </c>
-      <c r="O14">
+      <c r="P14">
         <v>0.801615635858253</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>0.808403535323903</v>
       </c>
     </row>
@@ -1119,48 +1163,51 @@
         </is>
       </c>
       <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
         <v>0.2860385879613659</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>0.4243966139277334</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <v>0.514824167066633</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>0.5502066468121639</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>0.6062202455155794</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>0.6155984523071043</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>0.6469192351053643</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>0.670311733981125</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>0.6886098629741283</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <v>0.7057344200818807</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>0.7381142606479547</v>
       </c>
-      <c r="M15">
+      <c r="N15">
         <v>0.7693931873636753</v>
       </c>
-      <c r="N15">
+      <c r="O15">
         <v>0.7786166663727971</v>
       </c>
-      <c r="O15">
+      <c r="P15">
         <v>0.7909897215264828</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>0.7983878981043133</v>
       </c>
     </row>
@@ -1171,48 +1218,51 @@
         </is>
       </c>
       <c r="B16">
+        <v>0</v>
+      </c>
+      <c r="C16">
         <v>0.2860117304978392</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>0.4243870817737677</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <v>0.5147162369262204</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>0.5499864117382017</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>0.6057151142684936</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>0.6149464887897105</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>0.6463781112343139</v>
       </c>
-      <c r="I16">
+      <c r="J16">
         <v>0.6699003997281414</v>
       </c>
-      <c r="J16">
+      <c r="K16">
         <v>0.6880913694235733</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.705183401080581</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.7378592709500791</v>
       </c>
-      <c r="M16">
+      <c r="N16">
         <v>0.7688972058755973</v>
       </c>
-      <c r="N16">
+      <c r="O16">
         <v>0.7785799319339183</v>
       </c>
-      <c r="O16">
+      <c r="P16">
         <v>0.7910422351275503</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>0.7976726844211319</v>
       </c>
     </row>
@@ -1223,48 +1273,51 @@
         </is>
       </c>
       <c r="B17">
+        <v>0</v>
+      </c>
+      <c r="C17">
         <v>0.2859498724737843</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>0.424405534806751</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <v>0.5147364980066882</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>0.5500591416862686</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>0.6057825339903551</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>0.6149143405026452</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>0.6462098595705308</v>
       </c>
-      <c r="I17">
+      <c r="J17">
         <v>0.6692177559989428</v>
       </c>
-      <c r="J17">
+      <c r="K17">
         <v>0.6868522079807469</v>
       </c>
-      <c r="K17">
+      <c r="L17">
         <v>0.7035520336764817</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>0.7366871123339744</v>
       </c>
-      <c r="M17">
+      <c r="N17">
         <v>0.7673840610139171</v>
       </c>
-      <c r="N17">
+      <c r="O17">
         <v>0.7791952634563866</v>
       </c>
-      <c r="O17">
+      <c r="P17">
         <v>0.7899007072610965</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>0.796161727758426</v>
       </c>
     </row>
@@ -1275,48 +1328,51 @@
         </is>
       </c>
       <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
         <v>0.416527372805893</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>0.4568582659615227</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <v>0.4891003666621635</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <v>0.536558021421444</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>0.6065513228685848</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>0.6881631289064578</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.7356562356784468</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>0.7546241935874763</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.7791677226487207</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>0.7960337537552628</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.8278783900254942</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>0.8454297045862966</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.8624203469946596</v>
       </c>
-      <c r="O18">
+      <c r="P18">
         <v>0.8720218220924337</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>0.8895549793027252</v>
       </c>
     </row>
@@ -1327,48 +1383,51 @@
         </is>
       </c>
       <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
         <v>0.416988101837615</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>0.4634905377677555</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <v>0.4913793153050963</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>0.5538374355964806</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>0.6343107491796502</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.662630148904095</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.7271074136101405</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.7575818993788919</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.7711784260342288</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.7885349746238852</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.8088513399021593</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>0.8332649726721177</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.8512542163415823</v>
       </c>
-      <c r="O19">
+      <c r="P19">
         <v>0.8655082492413771</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>0.8812070172921141</v>
       </c>
     </row>
@@ -1379,48 +1438,51 @@
         </is>
       </c>
       <c r="B20">
+        <v>0</v>
+      </c>
+      <c r="C20">
         <v>0.4142143791506914</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>0.4499528712084835</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <v>0.5074036596526625</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <v>0.5467055534622571</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>0.6193888422738587</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.672807882014835</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.7163693873939095</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>0.7342327335036486</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.755954147841349</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>0.7725602372154518</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.7919541243303284</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>0.8118736141733346</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.8311989664569577</v>
       </c>
-      <c r="O20">
+      <c r="P20">
         <v>0.8496625860330992</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>0.8670684113649234</v>
       </c>
     </row>
@@ -1431,48 +1493,51 @@
         </is>
       </c>
       <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>0.3413873006610957</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>0.4363948250722492</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <v>0.4858370902677622</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <v>0.5570949244768917</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>0.5888458193170603</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <v>0.6517090143756297</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <v>0.6868202930067993</v>
       </c>
-      <c r="I21">
+      <c r="J21">
         <v>0.7266360269992008</v>
       </c>
-      <c r="J21">
+      <c r="K21">
         <v>0.7506385580594471</v>
       </c>
-      <c r="K21">
+      <c r="L21">
         <v>0.7697241689430112</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>0.8016538483560512</v>
       </c>
-      <c r="M21">
+      <c r="N21">
         <v>0.8221960527935704</v>
       </c>
-      <c r="N21">
+      <c r="O21">
         <v>0.8472617169022794</v>
       </c>
-      <c r="O21">
+      <c r="P21">
         <v>0.865362475364406</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>0.8758068804340416</v>
       </c>
     </row>
@@ -1483,48 +1548,51 @@
         </is>
       </c>
       <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>0.3406548136742229</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>0.4359349938866528</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>0.4836973548920916</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>0.5527486829087397</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>0.5865268460498358</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <v>0.6478484529898231</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>0.6797212413836888</v>
       </c>
-      <c r="I22">
+      <c r="J22">
         <v>0.723016113753135</v>
       </c>
-      <c r="J22">
+      <c r="K22">
         <v>0.7440493725725423</v>
       </c>
-      <c r="K22">
+      <c r="L22">
         <v>0.771555722192235</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>0.8036551748222449</v>
       </c>
-      <c r="M22">
+      <c r="N22">
         <v>0.8227577367527383</v>
       </c>
-      <c r="N22">
+      <c r="O22">
         <v>0.8424040928421908</v>
       </c>
-      <c r="O22">
+      <c r="P22">
         <v>0.8608984686376722</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>0.8755324360155954</v>
       </c>
     </row>
@@ -1535,1296 +1603,1151 @@
         </is>
       </c>
       <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>0.4152365205379869</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>0.5105125935352841</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <v>0.5314361500808222</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>0.562784988661726</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>0.601321586964162</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <v>0.6552912707021661</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <v>0.6928933461916581</v>
       </c>
-      <c r="I23">
+      <c r="J23">
         <v>0.7306987957062947</v>
       </c>
-      <c r="J23">
+      <c r="K23">
         <v>0.7657791526555151</v>
       </c>
-      <c r="K23">
+      <c r="L23">
         <v>0.8083397933983362</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>0.8461035636073262</v>
       </c>
-      <c r="M23">
+      <c r="N23">
         <v>0.8785616725479833</v>
       </c>
-      <c r="N23">
+      <c r="O23">
         <v>0.8901421559349101</v>
       </c>
-      <c r="O23">
+      <c r="P23">
         <v>0.9042472407069174</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>0.9177234621741354</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
         </is>
       </c>
       <c r="B24">
-        <v>0.07434771376962812</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0.1147239097132151</v>
+        <v>0.3999470774631368</v>
       </c>
       <c r="D24">
-        <v>0.1568488952345829</v>
+        <v>0.4711134866252146</v>
       </c>
       <c r="E24">
-        <v>0.2285482583820578</v>
+        <v>0.5246965765693318</v>
       </c>
       <c r="F24">
-        <v>0.3047853633828888</v>
+        <v>0.5500669293372182</v>
       </c>
       <c r="G24">
-        <v>0.4118349398320148</v>
+        <v>0.5620038608096954</v>
       </c>
       <c r="H24">
-        <v>0.4574641315947388</v>
+        <v>0.5883442226549134</v>
       </c>
       <c r="I24">
-        <v>0.5256972356818207</v>
+        <v>0.6749468753415107</v>
       </c>
       <c r="J24">
-        <v>0.5796703930491879</v>
+        <v>0.7386929626882287</v>
       </c>
       <c r="K24">
-        <v>0.6568435671737559</v>
+        <v>0.7558565817322753</v>
       </c>
       <c r="L24">
-        <v>0.7082035973531703</v>
+        <v>0.8009126297171658</v>
       </c>
       <c r="M24">
-        <v>0.7729089028955251</v>
+        <v>0.8276053574529006</v>
       </c>
       <c r="N24">
-        <v>0.8237025654788982</v>
+        <v>0.867012194809772</v>
       </c>
       <c r="O24">
-        <v>0.8598693953840116</v>
+        <v>0.8955112512925033</v>
       </c>
       <c r="P24">
-        <v>0.8796990883537816</v>
+        <v>0.9136252684440587</v>
+      </c>
+      <c r="Q24">
+        <v>0.9200975926964148</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adj_red_c(950,20,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.08303342110517287</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>0.1352438262379504</v>
+        <v>0.3997640313695494</v>
       </c>
       <c r="D25">
-        <v>0.1766654256061068</v>
+        <v>0.4726949992792367</v>
       </c>
       <c r="E25">
-        <v>0.2758077324073146</v>
+        <v>0.531752194114902</v>
       </c>
       <c r="F25">
-        <v>0.3221874468608139</v>
+        <v>0.5589315274917346</v>
       </c>
       <c r="G25">
-        <v>0.3948807451898754</v>
+        <v>0.5911726037416527</v>
       </c>
       <c r="H25">
-        <v>0.5025422816532689</v>
+        <v>0.6113427592227434</v>
       </c>
       <c r="I25">
-        <v>0.5655451266051363</v>
+        <v>0.6365625795147904</v>
       </c>
       <c r="J25">
-        <v>0.6182688604101397</v>
+        <v>0.7020421276873683</v>
       </c>
       <c r="K25">
-        <v>0.6907445290256279</v>
+        <v>0.7270673902273737</v>
       </c>
       <c r="L25">
-        <v>0.7296402368904026</v>
+        <v>0.7850860438587626</v>
       </c>
       <c r="M25">
-        <v>0.7553281679318072</v>
+        <v>0.8120030735161153</v>
       </c>
       <c r="N25">
-        <v>0.8020488815064819</v>
+        <v>0.8464868757379249</v>
       </c>
       <c r="O25">
-        <v>0.830788302980526</v>
+        <v>0.8810685975245593</v>
       </c>
       <c r="P25">
-        <v>0.8596084016139394</v>
+        <v>0.9056470036740742</v>
+      </c>
+      <c r="Q25">
+        <v>0.9131067712216276</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
         </is>
       </c>
       <c r="B26">
-        <v>0.06859689707034555</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0.08221351188743153</v>
+        <v>0.4099685767214993</v>
       </c>
       <c r="D26">
-        <v>0.09431126710183113</v>
+        <v>0.4642101904027026</v>
       </c>
       <c r="E26">
-        <v>0.1462096491615084</v>
+        <v>0.5344400945013056</v>
       </c>
       <c r="F26">
-        <v>0.2766638102954154</v>
+        <v>0.5515681281950069</v>
       </c>
       <c r="G26">
-        <v>0.3119131652712087</v>
+        <v>0.5598725089592402</v>
       </c>
       <c r="H26">
-        <v>0.342326186220141</v>
+        <v>0.6083242222346884</v>
       </c>
       <c r="I26">
-        <v>0.4134021002660877</v>
+        <v>0.6667378838815463</v>
       </c>
       <c r="J26">
-        <v>0.4445880417359691</v>
+        <v>0.6980517858894568</v>
       </c>
       <c r="K26">
-        <v>0.4940347460142449</v>
+        <v>0.780536803657446</v>
       </c>
       <c r="L26">
-        <v>0.5185935797244727</v>
+        <v>0.817233987620811</v>
       </c>
       <c r="M26">
-        <v>0.5634548933012431</v>
+        <v>0.8413147422660706</v>
       </c>
       <c r="N26">
-        <v>0.603558821341039</v>
+        <v>0.8698426196974616</v>
       </c>
       <c r="O26">
-        <v>0.6489423362679712</v>
+        <v>0.8922492622375671</v>
       </c>
       <c r="P26">
-        <v>0.6732735909679511</v>
+        <v>0.9125148469586384</v>
+      </c>
+      <c r="Q26">
+        <v>0.9274613914087398</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>adj_red_c(950,750,1)_snv_sder_c(2,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.06954304710746961</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>0.08816275714075406</v>
+        <v>0.4099168878782059</v>
       </c>
       <c r="D27">
-        <v>0.2164580792227812</v>
+        <v>0.4635857623080076</v>
       </c>
       <c r="E27">
-        <v>0.2421329990957358</v>
+        <v>0.5329494739439193</v>
       </c>
       <c r="F27">
-        <v>0.3190243758737272</v>
+        <v>0.544333018176405</v>
       </c>
       <c r="G27">
-        <v>0.3797883547475726</v>
+        <v>0.5508134385760245</v>
       </c>
       <c r="H27">
-        <v>0.4211757650580285</v>
+        <v>0.5792029174428116</v>
       </c>
       <c r="I27">
-        <v>0.4781450511858122</v>
+        <v>0.6202750479650576</v>
       </c>
       <c r="J27">
-        <v>0.5538923065042838</v>
+        <v>0.6461283952018457</v>
       </c>
       <c r="K27">
-        <v>0.5784474117937397</v>
+        <v>0.6950145231036675</v>
       </c>
       <c r="L27">
-        <v>0.5957511997171955</v>
+        <v>0.7364088231224927</v>
       </c>
       <c r="M27">
-        <v>0.643606306223159</v>
+        <v>0.7516685000649462</v>
       </c>
       <c r="N27">
-        <v>0.6777781666904747</v>
+        <v>0.769024475522087</v>
       </c>
       <c r="O27">
-        <v>0.7207247242504521</v>
+        <v>0.8176163253343672</v>
       </c>
       <c r="P27">
-        <v>0.7499006708778001</v>
+        <v>0.8376388666233798</v>
+      </c>
+      <c r="Q27">
+        <v>0.8452370737348572</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
         </is>
       </c>
       <c r="B28">
-        <v>0.3999470774631368</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>0.4711134866252146</v>
+        <v>0.3996656229160285</v>
       </c>
       <c r="D28">
-        <v>0.5246965765693318</v>
+        <v>0.4720994724954327</v>
       </c>
       <c r="E28">
-        <v>0.5500669293372182</v>
+        <v>0.5300870742457027</v>
       </c>
       <c r="F28">
-        <v>0.5620038608096954</v>
+        <v>0.5569456762175571</v>
       </c>
       <c r="G28">
-        <v>0.5883442226549134</v>
+        <v>0.5809462609146476</v>
       </c>
       <c r="H28">
-        <v>0.6749468753415107</v>
+        <v>0.5936754708675731</v>
       </c>
       <c r="I28">
-        <v>0.7386929626882287</v>
+        <v>0.6090938226933055</v>
       </c>
       <c r="J28">
-        <v>0.7558565817322753</v>
+        <v>0.6564009339426887</v>
       </c>
       <c r="K28">
-        <v>0.8009126297171658</v>
+        <v>0.6734495923169128</v>
       </c>
       <c r="L28">
-        <v>0.8276053574529006</v>
+        <v>0.7202791807316016</v>
       </c>
       <c r="M28">
-        <v>0.867012194809772</v>
+        <v>0.7461486865687316</v>
       </c>
       <c r="N28">
-        <v>0.8955112512925033</v>
+        <v>0.7655229095270821</v>
       </c>
       <c r="O28">
-        <v>0.9136252684440587</v>
+        <v>0.7973752906965709</v>
       </c>
       <c r="P28">
-        <v>0.9200975926964148</v>
+        <v>0.8254125134327299</v>
+      </c>
+      <c r="Q28">
+        <v>0.8364750808626051</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
         </is>
       </c>
       <c r="B29">
-        <v>0.3997640313695494</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <v>0.4726949992792367</v>
+        <v>0.3996022475986146</v>
       </c>
       <c r="D29">
-        <v>0.531752194114902</v>
+        <v>0.472127964635073</v>
       </c>
       <c r="E29">
-        <v>0.5589315274917346</v>
+        <v>0.5300972281974811</v>
       </c>
       <c r="F29">
-        <v>0.5911726037416527</v>
+        <v>0.5570142396045166</v>
       </c>
       <c r="G29">
-        <v>0.6113427592227434</v>
+        <v>0.5810026124189784</v>
       </c>
       <c r="H29">
-        <v>0.6365625795147904</v>
+        <v>0.5935004053988868</v>
       </c>
       <c r="I29">
-        <v>0.7020421276873683</v>
+        <v>0.6087805312439918</v>
       </c>
       <c r="J29">
-        <v>0.7270673902273737</v>
+        <v>0.6563192407206798</v>
       </c>
       <c r="K29">
-        <v>0.7850860438587626</v>
+        <v>0.6736185963559992</v>
       </c>
       <c r="L29">
-        <v>0.8120030735161153</v>
+        <v>0.7174758992304096</v>
       </c>
       <c r="M29">
-        <v>0.8464868757379249</v>
+        <v>0.7433305840525016</v>
       </c>
       <c r="N29">
-        <v>0.8810685975245593</v>
+        <v>0.7624691801344066</v>
       </c>
       <c r="O29">
-        <v>0.9056470036740742</v>
+        <v>0.7893548561226189</v>
       </c>
       <c r="P29">
-        <v>0.9131067712216276</v>
+        <v>0.8081515103443956</v>
+      </c>
+      <c r="Q29">
+        <v>0.8258139544646971</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.4099685767214993</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>0.4642101904027026</v>
+        <v>0.3995437739475189</v>
       </c>
       <c r="D30">
-        <v>0.5344400945013056</v>
+        <v>0.4720593609055822</v>
       </c>
       <c r="E30">
-        <v>0.5515681281950069</v>
+        <v>0.5299054592413679</v>
       </c>
       <c r="F30">
-        <v>0.5598725089592402</v>
+        <v>0.5567698306948932</v>
       </c>
       <c r="G30">
-        <v>0.6083242222346884</v>
+        <v>0.5802792679837188</v>
       </c>
       <c r="H30">
-        <v>0.6667378838815463</v>
+        <v>0.5921809871372332</v>
       </c>
       <c r="I30">
-        <v>0.6980517858894568</v>
+        <v>0.606940853215624</v>
       </c>
       <c r="J30">
-        <v>0.780536803657446</v>
+        <v>0.6538708740409163</v>
       </c>
       <c r="K30">
-        <v>0.817233987620811</v>
+        <v>0.6711677333850667</v>
       </c>
       <c r="L30">
-        <v>0.8413147422660706</v>
+        <v>0.7144399178547238</v>
       </c>
       <c r="M30">
-        <v>0.8698426196974616</v>
+        <v>0.7403738351797915</v>
       </c>
       <c r="N30">
-        <v>0.8922492622375671</v>
+        <v>0.7593040842810561</v>
       </c>
       <c r="O30">
-        <v>0.9125148469586384</v>
+        <v>0.7846638299868117</v>
       </c>
       <c r="P30">
-        <v>0.9274613914087398</v>
+        <v>0.7986060959418811</v>
+      </c>
+      <c r="Q30">
+        <v>0.8226785309256811</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.4099168878782059</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>0.4635857623080076</v>
+        <v>0.3994088463773</v>
       </c>
       <c r="D31">
-        <v>0.5329494739439193</v>
+        <v>0.4719750476688386</v>
       </c>
       <c r="E31">
-        <v>0.544333018176405</v>
+        <v>0.5296745355967104</v>
       </c>
       <c r="F31">
-        <v>0.5508134385760245</v>
+        <v>0.5565816585435854</v>
       </c>
       <c r="G31">
-        <v>0.5792029174428116</v>
+        <v>0.579623266758224</v>
       </c>
       <c r="H31">
-        <v>0.6202750479650576</v>
+        <v>0.5907503095664238</v>
       </c>
       <c r="I31">
-        <v>0.6461283952018457</v>
+        <v>0.6049064888093989</v>
       </c>
       <c r="J31">
-        <v>0.6950145231036675</v>
+        <v>0.6507710954007747</v>
       </c>
       <c r="K31">
-        <v>0.7364088231224927</v>
+        <v>0.6684701582141835</v>
       </c>
       <c r="L31">
-        <v>0.7516685000649462</v>
+        <v>0.70998494764956</v>
       </c>
       <c r="M31">
-        <v>0.769024475522087</v>
+        <v>0.7373160639275542</v>
       </c>
       <c r="N31">
-        <v>0.8176163253343672</v>
+        <v>0.7561472415226305</v>
       </c>
       <c r="O31">
-        <v>0.8376388666233798</v>
+        <v>0.7747684374032737</v>
       </c>
       <c r="P31">
-        <v>0.8452370737348572</v>
+        <v>0.7897897741893937</v>
+      </c>
+      <c r="Q31">
+        <v>0.8191249922047467</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.3996656229160285</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>0.4720994724954327</v>
+        <v>0.3997358061173576</v>
       </c>
       <c r="D32">
-        <v>0.5300870742457027</v>
+        <v>0.472267692542286</v>
       </c>
       <c r="E32">
-        <v>0.5569456762175571</v>
+        <v>0.530575692273664</v>
       </c>
       <c r="F32">
-        <v>0.5809462609146476</v>
+        <v>0.55751386426881</v>
       </c>
       <c r="G32">
-        <v>0.5936754708675731</v>
+        <v>0.58280728760342</v>
       </c>
       <c r="H32">
-        <v>0.6090938226933055</v>
+        <v>0.5967345579278007</v>
       </c>
       <c r="I32">
-        <v>0.6564009339426887</v>
+        <v>0.6129671324712196</v>
       </c>
       <c r="J32">
-        <v>0.6734495923169128</v>
+        <v>0.6600937025332206</v>
       </c>
       <c r="K32">
-        <v>0.7202791807316016</v>
+        <v>0.6769707838602533</v>
       </c>
       <c r="L32">
-        <v>0.7461486865687316</v>
+        <v>0.7226818566807707</v>
       </c>
       <c r="M32">
-        <v>0.7655229095270821</v>
+        <v>0.7489218186665496</v>
       </c>
       <c r="N32">
-        <v>0.7973752906965709</v>
+        <v>0.7708273653280935</v>
       </c>
       <c r="O32">
-        <v>0.8254125134327299</v>
+        <v>0.8074400770466668</v>
       </c>
       <c r="P32">
-        <v>0.8364750808626051</v>
+        <v>0.828823011202011</v>
+      </c>
+      <c r="Q32">
+        <v>0.8497529478405687</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.3996022475986146</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>0.472127964635073</v>
+        <v>0.3997221313734672</v>
       </c>
       <c r="D33">
-        <v>0.5300972281974811</v>
+        <v>0.4722496396640133</v>
       </c>
       <c r="E33">
-        <v>0.5570142396045166</v>
+        <v>0.5305227169794708</v>
       </c>
       <c r="F33">
-        <v>0.5810026124189784</v>
+        <v>0.5574613060594256</v>
       </c>
       <c r="G33">
-        <v>0.5935004053988868</v>
+        <v>0.5825530369347076</v>
       </c>
       <c r="H33">
-        <v>0.6087805312439918</v>
+        <v>0.5962454376236435</v>
       </c>
       <c r="I33">
-        <v>0.6563192407206798</v>
+        <v>0.6122518391865204</v>
       </c>
       <c r="J33">
-        <v>0.6736185963559992</v>
+        <v>0.6595772377620928</v>
       </c>
       <c r="K33">
-        <v>0.7174758992304096</v>
+        <v>0.6765085659613337</v>
       </c>
       <c r="L33">
-        <v>0.7433305840525016</v>
+        <v>0.7221815652603913</v>
       </c>
       <c r="M33">
-        <v>0.7624691801344066</v>
+        <v>0.7489016111877174</v>
       </c>
       <c r="N33">
-        <v>0.7893548561226189</v>
+        <v>0.7706575199686438</v>
       </c>
       <c r="O33">
-        <v>0.8081515103443956</v>
+        <v>0.8039222461899882</v>
       </c>
       <c r="P33">
-        <v>0.8258139544646971</v>
+        <v>0.826352504444979</v>
+      </c>
+      <c r="Q33">
+        <v>0.8480281704939343</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
         </is>
       </c>
       <c r="B34">
-        <v>0.3995437739475189</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>0.4720593609055822</v>
+        <v>0.3997066861099703</v>
       </c>
       <c r="D34">
-        <v>0.5299054592413679</v>
+        <v>0.4722675936985982</v>
       </c>
       <c r="E34">
-        <v>0.5567698306948932</v>
+        <v>0.5305208860460374</v>
       </c>
       <c r="F34">
-        <v>0.5802792679837188</v>
+        <v>0.5574585186119358</v>
       </c>
       <c r="G34">
-        <v>0.5921809871372332</v>
+        <v>0.582379912589178</v>
       </c>
       <c r="H34">
-        <v>0.606940853215624</v>
+        <v>0.595780978554062</v>
       </c>
       <c r="I34">
-        <v>0.6538708740409163</v>
+        <v>0.6114140194069893</v>
       </c>
       <c r="J34">
-        <v>0.6711677333850667</v>
+        <v>0.6579610785711181</v>
       </c>
       <c r="K34">
-        <v>0.7144399178547238</v>
+        <v>0.6747150358931058</v>
       </c>
       <c r="L34">
-        <v>0.7403738351797915</v>
+        <v>0.7198294620522352</v>
       </c>
       <c r="M34">
-        <v>0.7593040842810561</v>
+        <v>0.7471196170974096</v>
       </c>
       <c r="N34">
-        <v>0.7846638299868117</v>
+        <v>0.768447194136749</v>
       </c>
       <c r="O34">
-        <v>0.7986060959418811</v>
+        <v>0.7983341676343799</v>
       </c>
       <c r="P34">
-        <v>0.8226785309256811</v>
+        <v>0.8210924834291331</v>
+      </c>
+      <c r="Q34">
+        <v>0.8450646861233098</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.3994088463773</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0.4719750476688386</v>
+        <v>0.3996898196162351</v>
       </c>
       <c r="D35">
-        <v>0.5296745355967104</v>
+        <v>0.4723321550289542</v>
       </c>
       <c r="E35">
-        <v>0.5565816585435854</v>
+        <v>0.5306213253375902</v>
       </c>
       <c r="F35">
-        <v>0.579623266758224</v>
+        <v>0.5575633097942057</v>
       </c>
       <c r="G35">
-        <v>0.5907503095664238</v>
+        <v>0.5824790378671048</v>
       </c>
       <c r="H35">
-        <v>0.6049064888093989</v>
+        <v>0.5957107932928947</v>
       </c>
       <c r="I35">
-        <v>0.6507710954007747</v>
+        <v>0.6111638252005391</v>
       </c>
       <c r="J35">
-        <v>0.6684701582141835</v>
+        <v>0.6579237977729212</v>
       </c>
       <c r="K35">
-        <v>0.70998494764956</v>
+        <v>0.6747192299336728</v>
       </c>
       <c r="L35">
-        <v>0.7373160639275542</v>
+        <v>0.7190653151228499</v>
       </c>
       <c r="M35">
-        <v>0.7561472415226305</v>
+        <v>0.7464600720522745</v>
       </c>
       <c r="N35">
-        <v>0.7747684374032737</v>
+        <v>0.7674068396499398</v>
       </c>
       <c r="O35">
-        <v>0.7897897741893937</v>
+        <v>0.7945868878107588</v>
       </c>
       <c r="P35">
-        <v>0.8191249922047467</v>
+        <v>0.8219405582075822</v>
+      </c>
+      <c r="Q35">
+        <v>0.8375911110647797</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.3997358061173576</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0.472267692542286</v>
+        <v>0.3994575396960341</v>
       </c>
       <c r="D36">
-        <v>0.530575692273664</v>
+        <v>0.4723799646236485</v>
       </c>
       <c r="E36">
-        <v>0.55751386426881</v>
+        <v>0.5303571712718631</v>
       </c>
       <c r="F36">
-        <v>0.58280728760342</v>
+        <v>0.5573139459648087</v>
       </c>
       <c r="G36">
-        <v>0.5967345579278007</v>
+        <v>0.581060294663659</v>
       </c>
       <c r="H36">
-        <v>0.6129671324712196</v>
+        <v>0.5922742958384832</v>
       </c>
       <c r="I36">
-        <v>0.6600937025332206</v>
+        <v>0.6064094678541045</v>
       </c>
       <c r="J36">
-        <v>0.6769707838602533</v>
+        <v>0.6517175820937204</v>
       </c>
       <c r="K36">
-        <v>0.7226818566807707</v>
+        <v>0.6692578489185286</v>
       </c>
       <c r="L36">
-        <v>0.7489218186665496</v>
+        <v>0.7077533988745091</v>
       </c>
       <c r="M36">
-        <v>0.7708273653280935</v>
+        <v>0.7361696166174725</v>
       </c>
       <c r="N36">
-        <v>0.8074400770466668</v>
+        <v>0.7566058536155582</v>
       </c>
       <c r="O36">
-        <v>0.828823011202011</v>
+        <v>0.7750260365623984</v>
       </c>
       <c r="P36">
-        <v>0.8497529478405687</v>
+        <v>0.787151895476589</v>
+      </c>
+      <c r="Q36">
+        <v>0.8183112732891016</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
         </is>
       </c>
       <c r="B37">
-        <v>0.3997221313734672</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>0.4722496396640133</v>
+        <v>0.4201886271451944</v>
       </c>
       <c r="D37">
-        <v>0.5305227169794708</v>
+        <v>0.5643655399833056</v>
       </c>
       <c r="E37">
-        <v>0.5574613060594256</v>
+        <v>0.5825394436712341</v>
       </c>
       <c r="F37">
-        <v>0.5825530369347076</v>
+        <v>0.602586344716286</v>
       </c>
       <c r="G37">
-        <v>0.5962454376236435</v>
+        <v>0.6399924209883114</v>
       </c>
       <c r="H37">
-        <v>0.6122518391865204</v>
+        <v>0.7086054652686598</v>
       </c>
       <c r="I37">
-        <v>0.6595772377620928</v>
+        <v>0.7612834453906815</v>
       </c>
       <c r="J37">
-        <v>0.6765085659613337</v>
+        <v>0.7772986844016201</v>
       </c>
       <c r="K37">
-        <v>0.7221815652603913</v>
+        <v>0.8054397531690993</v>
       </c>
       <c r="L37">
-        <v>0.7489016111877174</v>
+        <v>0.8290114723016416</v>
       </c>
       <c r="M37">
-        <v>0.7706575199686438</v>
+        <v>0.8549877951586222</v>
       </c>
       <c r="N37">
-        <v>0.8039222461899882</v>
+        <v>0.8755167972803143</v>
       </c>
       <c r="O37">
-        <v>0.826352504444979</v>
+        <v>0.8891350612121677</v>
       </c>
       <c r="P37">
-        <v>0.8480281704939343</v>
+        <v>0.89704463619956</v>
+      </c>
+      <c r="Q37">
+        <v>0.9053224699602724</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
         </is>
       </c>
       <c r="B38">
-        <v>0.3997066861099703</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>0.4722675936985982</v>
+        <v>0.4201710801530821</v>
       </c>
       <c r="D38">
-        <v>0.5305208860460374</v>
+        <v>0.5536787353509001</v>
       </c>
       <c r="E38">
-        <v>0.5574585186119358</v>
+        <v>0.5670314940252941</v>
       </c>
       <c r="F38">
-        <v>0.582379912589178</v>
+        <v>0.5870520270002131</v>
       </c>
       <c r="G38">
-        <v>0.595780978554062</v>
+        <v>0.6278829934598433</v>
       </c>
       <c r="H38">
-        <v>0.6114140194069893</v>
+        <v>0.6700578624008628</v>
       </c>
       <c r="I38">
-        <v>0.6579610785711181</v>
+        <v>0.7152688660994815</v>
       </c>
       <c r="J38">
-        <v>0.6747150358931058</v>
+        <v>0.7367245092074446</v>
       </c>
       <c r="K38">
-        <v>0.7198294620522352</v>
+        <v>0.7879162967567042</v>
       </c>
       <c r="L38">
-        <v>0.7471196170974096</v>
+        <v>0.8219799966768641</v>
       </c>
       <c r="M38">
-        <v>0.768447194136749</v>
+        <v>0.8505302251775051</v>
       </c>
       <c r="N38">
-        <v>0.7983341676343799</v>
+        <v>0.8542657468451398</v>
       </c>
       <c r="O38">
-        <v>0.8210924834291331</v>
+        <v>0.871557470789208</v>
       </c>
       <c r="P38">
-        <v>0.8450646861233098</v>
+        <v>0.888355594474493</v>
+      </c>
+      <c r="Q38">
+        <v>0.8983020920801512</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.3996898196162351</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>0.4723321550289542</v>
+        <v>0.4208396661073317</v>
       </c>
       <c r="D39">
-        <v>0.5306213253375902</v>
+        <v>0.5550981345502379</v>
       </c>
       <c r="E39">
-        <v>0.5575633097942057</v>
+        <v>0.5669701306784142</v>
       </c>
       <c r="F39">
-        <v>0.5824790378671048</v>
+        <v>0.5926076635311779</v>
       </c>
       <c r="G39">
-        <v>0.5957107932928947</v>
+        <v>0.6217605741822191</v>
       </c>
       <c r="H39">
-        <v>0.6111638252005391</v>
+        <v>0.6504361736240067</v>
       </c>
       <c r="I39">
-        <v>0.6579237977729212</v>
+        <v>0.707997213011279</v>
       </c>
       <c r="J39">
-        <v>0.6747192299336728</v>
+        <v>0.7293856813763362</v>
       </c>
       <c r="K39">
-        <v>0.7190653151228499</v>
+        <v>0.7625236477648095</v>
       </c>
       <c r="L39">
-        <v>0.7464600720522745</v>
+        <v>0.785666028231666</v>
       </c>
       <c r="M39">
-        <v>0.7674068396499398</v>
+        <v>0.8177867448506837</v>
       </c>
       <c r="N39">
-        <v>0.7945868878107588</v>
+        <v>0.8302799393680044</v>
       </c>
       <c r="O39">
-        <v>0.8219405582075822</v>
+        <v>0.8459691773419986</v>
       </c>
       <c r="P39">
-        <v>0.8375911110647797</v>
+        <v>0.8602344497480485</v>
+      </c>
+      <c r="Q39">
+        <v>0.8794038418057147</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
         </is>
       </c>
       <c r="B40">
-        <v>0.3994575396960341</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0.4723799646236485</v>
+        <v>0.4069125874919396</v>
       </c>
       <c r="D40">
-        <v>0.5303571712718631</v>
+        <v>0.4502023723661338</v>
       </c>
       <c r="E40">
-        <v>0.5573139459648087</v>
+        <v>0.5152473890698988</v>
       </c>
       <c r="F40">
-        <v>0.581060294663659</v>
+        <v>0.5488330846130336</v>
       </c>
       <c r="G40">
-        <v>0.5922742958384832</v>
+        <v>0.6463580924444943</v>
       </c>
       <c r="H40">
-        <v>0.6064094678541045</v>
+        <v>0.7007337382316299</v>
       </c>
       <c r="I40">
-        <v>0.6517175820937204</v>
+        <v>0.7282378562094685</v>
       </c>
       <c r="J40">
-        <v>0.6692578489185286</v>
+        <v>0.7623964913055543</v>
       </c>
       <c r="K40">
-        <v>0.7077533988745091</v>
+        <v>0.7974980869269848</v>
       </c>
       <c r="L40">
-        <v>0.7361696166174725</v>
+        <v>0.8377131889599694</v>
       </c>
       <c r="M40">
-        <v>0.7566058536155582</v>
+        <v>0.8576853810377236</v>
       </c>
       <c r="N40">
-        <v>0.7750260365623984</v>
+        <v>0.8656034049265424</v>
       </c>
       <c r="O40">
-        <v>0.787151895476589</v>
+        <v>0.8748586505468698</v>
       </c>
       <c r="P40">
-        <v>0.8183112732891016</v>
+        <v>0.8829903195519007</v>
+      </c>
+      <c r="Q40">
+        <v>0.8961871514091608</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+          <t>adj_snv_sder_c(1,3,5)_</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.4201886271451944</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>0.5643655399833056</v>
+        <v>0.4210994958751824</v>
       </c>
       <c r="D41">
-        <v>0.5825394436712341</v>
+        <v>0.4931570866147597</v>
       </c>
       <c r="E41">
-        <v>0.602586344716286</v>
+        <v>0.5676929709719025</v>
       </c>
       <c r="F41">
-        <v>0.6399924209883114</v>
+        <v>0.627391497865057</v>
       </c>
       <c r="G41">
-        <v>0.7086054652686598</v>
+        <v>0.6811273871022334</v>
       </c>
       <c r="H41">
-        <v>0.7612834453906815</v>
+        <v>0.7212067317541335</v>
       </c>
       <c r="I41">
-        <v>0.7772986844016201</v>
+        <v>0.7494580030597634</v>
       </c>
       <c r="J41">
-        <v>0.8054397531690993</v>
+        <v>0.7833040301513053</v>
       </c>
       <c r="K41">
-        <v>0.8290114723016416</v>
+        <v>0.8056922339776682</v>
       </c>
       <c r="L41">
-        <v>0.8549877951586222</v>
+        <v>0.8295979923622246</v>
       </c>
       <c r="M41">
-        <v>0.8755167972803143</v>
+        <v>0.8548929153192963</v>
       </c>
       <c r="N41">
-        <v>0.8891350612121677</v>
+        <v>0.8796745831755726</v>
       </c>
       <c r="O41">
-        <v>0.89704463619956</v>
+        <v>0.8965597350839967</v>
       </c>
       <c r="P41">
-        <v>0.9053224699602724</v>
+        <v>0.9139048805238467</v>
+      </c>
+      <c r="Q41">
+        <v>0.9286342168919522</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+          <t>adj_snv_sder_c(2,3,15)_</t>
         </is>
       </c>
       <c r="B42">
-        <v>0.4201710801530821</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>0.5536787353509001</v>
+        <v>0.3380392717695927</v>
       </c>
       <c r="D42">
-        <v>0.5670314940252941</v>
+        <v>0.4474594488276294</v>
       </c>
       <c r="E42">
-        <v>0.5870520270002131</v>
+        <v>0.5136156921623154</v>
       </c>
       <c r="F42">
-        <v>0.6278829934598433</v>
+        <v>0.5863749931620824</v>
       </c>
       <c r="G42">
-        <v>0.6700578624008628</v>
+        <v>0.645385164447039</v>
       </c>
       <c r="H42">
-        <v>0.7152688660994815</v>
+        <v>0.6685642115499089</v>
       </c>
       <c r="I42">
-        <v>0.7367245092074446</v>
+        <v>0.7204208929362276</v>
       </c>
       <c r="J42">
-        <v>0.7879162967567042</v>
+        <v>0.750730074899326</v>
       </c>
       <c r="K42">
-        <v>0.8219799966768641</v>
+        <v>0.7800645917938238</v>
       </c>
       <c r="L42">
-        <v>0.8505302251775051</v>
+        <v>0.832748169400862</v>
       </c>
       <c r="M42">
-        <v>0.8542657468451398</v>
+        <v>0.8595665843611391</v>
       </c>
       <c r="N42">
-        <v>0.871557470789208</v>
+        <v>0.8910230969740482</v>
       </c>
       <c r="O42">
-        <v>0.888355594474493</v>
+        <v>0.9038443883804459</v>
       </c>
       <c r="P42">
-        <v>0.8983020920801512</v>
+        <v>0.9129938389209398</v>
+      </c>
+      <c r="Q42">
+        <v>0.9223197887949548</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.4208396661073317</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>0.5550981345502379</v>
+        <v>0.4217237166619977</v>
       </c>
       <c r="D43">
-        <v>0.5669701306784142</v>
+        <v>0.4948053268857378</v>
       </c>
       <c r="E43">
-        <v>0.5926076635311779</v>
+        <v>0.549236180668867</v>
       </c>
       <c r="F43">
-        <v>0.6217605741822191</v>
+        <v>0.6144653255061527</v>
       </c>
       <c r="G43">
-        <v>0.6504361736240067</v>
+        <v>0.6696440507648262</v>
       </c>
       <c r="H43">
-        <v>0.707997213011279</v>
+        <v>0.7037335939589681</v>
       </c>
       <c r="I43">
-        <v>0.7293856813763362</v>
+        <v>0.7381860176539968</v>
       </c>
       <c r="J43">
-        <v>0.7625236477648095</v>
+        <v>0.7793744384096741</v>
       </c>
       <c r="K43">
-        <v>0.785666028231666</v>
+        <v>0.8210673598618491</v>
       </c>
       <c r="L43">
-        <v>0.8177867448506837</v>
+        <v>0.8504696536440912</v>
       </c>
       <c r="M43">
-        <v>0.8302799393680044</v>
+        <v>0.8714379684125937</v>
       </c>
       <c r="N43">
-        <v>0.8459691773419986</v>
+        <v>0.8993010724246953</v>
       </c>
       <c r="O43">
-        <v>0.8602344497480485</v>
+        <v>0.9062650179324409</v>
       </c>
       <c r="P43">
-        <v>0.8794038418057147</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>0.4069125874919396</v>
-      </c>
-      <c r="C44">
-        <v>0.4502023723661338</v>
-      </c>
-      <c r="D44">
-        <v>0.5152473890698988</v>
-      </c>
-      <c r="E44">
-        <v>0.5488330846130336</v>
-      </c>
-      <c r="F44">
-        <v>0.6463580924444943</v>
-      </c>
-      <c r="G44">
-        <v>0.7007337382316299</v>
-      </c>
-      <c r="H44">
-        <v>0.7282378562094685</v>
-      </c>
-      <c r="I44">
-        <v>0.7623964913055543</v>
-      </c>
-      <c r="J44">
-        <v>0.7974980869269848</v>
-      </c>
-      <c r="K44">
-        <v>0.8377131889599694</v>
-      </c>
-      <c r="L44">
-        <v>0.8576853810377236</v>
-      </c>
-      <c r="M44">
-        <v>0.8656034049265424</v>
-      </c>
-      <c r="N44">
-        <v>0.8748586505468698</v>
-      </c>
-      <c r="O44">
-        <v>0.8829903195519007</v>
-      </c>
-      <c r="P44">
-        <v>0.8961871514091608</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(1,3,5)_</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>0.4210994958751824</v>
-      </c>
-      <c r="C45">
-        <v>0.4931570866147597</v>
-      </c>
-      <c r="D45">
-        <v>0.5676929709719025</v>
-      </c>
-      <c r="E45">
-        <v>0.627391497865057</v>
-      </c>
-      <c r="F45">
-        <v>0.6811273871022334</v>
-      </c>
-      <c r="G45">
-        <v>0.7212067317541335</v>
-      </c>
-      <c r="H45">
-        <v>0.7494580030597634</v>
-      </c>
-      <c r="I45">
-        <v>0.7833040301513053</v>
-      </c>
-      <c r="J45">
-        <v>0.8056922339776682</v>
-      </c>
-      <c r="K45">
-        <v>0.8295979923622246</v>
-      </c>
-      <c r="L45">
-        <v>0.8548929153192963</v>
-      </c>
-      <c r="M45">
-        <v>0.8796745831755726</v>
-      </c>
-      <c r="N45">
-        <v>0.8965597350839967</v>
-      </c>
-      <c r="O45">
-        <v>0.9139048805238467</v>
-      </c>
-      <c r="P45">
-        <v>0.9286342168919522</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>adj_snv_sder_c(2,3,15)_</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>0.3380392717695927</v>
-      </c>
-      <c r="C46">
-        <v>0.4474594488276294</v>
-      </c>
-      <c r="D46">
-        <v>0.5136156921623154</v>
-      </c>
-      <c r="E46">
-        <v>0.5863749931620824</v>
-      </c>
-      <c r="F46">
-        <v>0.645385164447039</v>
-      </c>
-      <c r="G46">
-        <v>0.6685642115499089</v>
-      </c>
-      <c r="H46">
-        <v>0.7204208929362276</v>
-      </c>
-      <c r="I46">
-        <v>0.750730074899326</v>
-      </c>
-      <c r="J46">
-        <v>0.7800645917938238</v>
-      </c>
-      <c r="K46">
-        <v>0.832748169400862</v>
-      </c>
-      <c r="L46">
-        <v>0.8595665843611391</v>
-      </c>
-      <c r="M46">
-        <v>0.8910230969740482</v>
-      </c>
-      <c r="N46">
-        <v>0.9038443883804459</v>
-      </c>
-      <c r="O46">
-        <v>0.9129938389209398</v>
-      </c>
-      <c r="P46">
-        <v>0.9223197887949548</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>0.4217237166619977</v>
-      </c>
-      <c r="C47">
-        <v>0.4948053268857378</v>
-      </c>
-      <c r="D47">
-        <v>0.549236180668867</v>
-      </c>
-      <c r="E47">
-        <v>0.6144653255061527</v>
-      </c>
-      <c r="F47">
-        <v>0.6696440507648262</v>
-      </c>
-      <c r="G47">
-        <v>0.7037335939589681</v>
-      </c>
-      <c r="H47">
-        <v>0.7381860176539968</v>
-      </c>
-      <c r="I47">
-        <v>0.7793744384096741</v>
-      </c>
-      <c r="J47">
-        <v>0.8210673598618491</v>
-      </c>
-      <c r="K47">
-        <v>0.8504696536440912</v>
-      </c>
-      <c r="L47">
-        <v>0.8714379684125937</v>
-      </c>
-      <c r="M47">
-        <v>0.8993010724246953</v>
-      </c>
-      <c r="N47">
-        <v>0.9062650179324409</v>
-      </c>
-      <c r="O47">
         <v>0.9260241880124095</v>
       </c>
-      <c r="P47">
+      <c r="Q43">
         <v>0.937110359846538</v>
       </c>
     </row>
